--- a/sinais_gerados/sinais_gerados_2026-08-24.xlsx
+++ b/sinais_gerados/sinais_gerados_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -571,25 +571,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>America MG</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>11</v>
+        <v>15.5</v>
       </c>
       <c r="G4" t="n">
-        <v>20</v>
+        <v>13.79</v>
       </c>
       <c r="H4" t="n">
         <v>200</v>
       </c>
       <c r="I4" t="n">
-        <v>19</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="5">
@@ -839,30 +839,30 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SPAIN 1</t>
+          <t>FRANCE 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>28.57</v>
+        <v>24.39</v>
       </c>
       <c r="H11" t="n">
         <v>200</v>
       </c>
       <c r="I11" t="n">
-        <v>27.14</v>
+        <v>23.17</v>
       </c>
     </row>
     <row r="12">
@@ -878,30 +878,30 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>FRANCE 2</t>
+          <t>ITALY 3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>24.39</v>
+        <v>25.64</v>
       </c>
       <c r="H12" t="n">
         <v>200</v>
       </c>
       <c r="I12" t="n">
-        <v>23.17</v>
+        <v>24.36</v>
       </c>
     </row>
     <row r="13">
@@ -917,30 +917,30 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ITALY 3</t>
+          <t>PORTUGAL 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>8.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="G13" t="n">
-        <v>25.64</v>
+        <v>35.71</v>
       </c>
       <c r="H13" t="n">
         <v>200</v>
       </c>
       <c r="I13" t="n">
-        <v>24.36</v>
+        <v>33.92</v>
       </c>
     </row>
     <row r="14">
@@ -956,30 +956,30 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PORTUGAL 1</t>
+          <t>BRAZIL 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>America MG</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="G14" t="n">
-        <v>35.71</v>
+        <v>30.3</v>
       </c>
       <c r="H14" t="n">
         <v>200</v>
       </c>
       <c r="I14" t="n">
-        <v>33.92</v>
+        <v>28.79</v>
       </c>
     </row>
     <row r="15">
@@ -990,35 +990,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lay 1x0</t>
+          <t>Lay 2x0</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BRAZIL 2</t>
+          <t>DENMARK 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Brondby</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>America MG</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>7.6</v>
+        <v>13.5</v>
       </c>
       <c r="G15" t="n">
-        <v>30.3</v>
+        <v>16</v>
       </c>
       <c r="H15" t="n">
         <v>200</v>
       </c>
       <c r="I15" t="n">
-        <v>28.79</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="16">
@@ -1034,30 +1034,30 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>DENMARK 1</t>
+          <t>SPAIN 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Brondby</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="G16" t="n">
-        <v>16</v>
+        <v>21.05</v>
       </c>
       <c r="H16" t="n">
         <v>200</v>
       </c>
       <c r="I16" t="n">
-        <v>15.2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -1073,30 +1073,30 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SPAIN 1</t>
+          <t>PORTUGAL 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="G17" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="H17" t="n">
         <v>200</v>
       </c>
       <c r="I17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18">
@@ -1112,30 +1112,30 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PORTUGAL 1</t>
+          <t>BRAZIL 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>America MG</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>20</v>
+        <v>22.22</v>
       </c>
       <c r="H18" t="n">
         <v>200</v>
       </c>
       <c r="I18" t="n">
-        <v>19</v>
+        <v>21.11</v>
       </c>
     </row>
     <row r="19">
@@ -1146,35 +1146,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Lay 2x0</t>
+          <t>Lay 0x3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BRAZIL 2</t>
+          <t>BULGARIA 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>America MG</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="G19" t="n">
-        <v>22.22</v>
+        <v>7.14</v>
       </c>
       <c r="H19" t="n">
         <v>200</v>
       </c>
       <c r="I19" t="n">
-        <v>21.11</v>
+        <v>6.78</v>
       </c>
     </row>
     <row r="20">
@@ -1190,30 +1190,30 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BULGARIA 1</t>
+          <t>SPAIN 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Celta Vigo B</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G20" t="n">
-        <v>7.14</v>
+        <v>6.06</v>
       </c>
       <c r="H20" t="n">
         <v>200</v>
       </c>
       <c r="I20" t="n">
-        <v>6.78</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="21">
@@ -1229,30 +1229,30 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SPAIN 2</t>
+          <t>BULGARIA 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Celta Vigo B</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G21" t="n">
-        <v>6.06</v>
+        <v>7.41</v>
       </c>
       <c r="H21" t="n">
         <v>200</v>
       </c>
       <c r="I21" t="n">
-        <v>5.76</v>
+        <v>7.04</v>
       </c>
     </row>
     <row r="22">
@@ -1268,30 +1268,30 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BULGARIA 1</t>
+          <t>COLOMBIA 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Leones FC</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Real Cartagena</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G22" t="n">
-        <v>7.41</v>
+        <v>6.06</v>
       </c>
       <c r="H22" t="n">
         <v>200</v>
       </c>
       <c r="I22" t="n">
-        <v>7.04</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="23">
@@ -1302,35 +1302,35 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Lay 0x3</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>COLOMBIA 2</t>
+          <t>SWEDEN 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Leones FC</t>
+          <t>Ostersunds FK</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Real Cartagena</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>34</v>
+        <v>16.5</v>
       </c>
       <c r="G23" t="n">
-        <v>6.06</v>
+        <v>12.9</v>
       </c>
       <c r="H23" t="n">
         <v>200</v>
       </c>
       <c r="I23" t="n">
-        <v>5.76</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="24">
@@ -1346,30 +1346,30 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SWEDEN 2</t>
+          <t>TURKEY 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Ostersunds FK</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Amed Sportif Faaliyetler</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="G24" t="n">
-        <v>12.9</v>
+        <v>10.81</v>
       </c>
       <c r="H24" t="n">
         <v>200</v>
       </c>
       <c r="I24" t="n">
-        <v>12.25</v>
+        <v>10.27</v>
       </c>
     </row>
     <row r="25">
@@ -1385,30 +1385,30 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>TURKEY 1</t>
+          <t>BRAZIL 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Botafogo FR</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Amed Sportif Faaliyetler</t>
+          <t>Athletico-PR</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="G25" t="n">
-        <v>10.81</v>
+        <v>11.76</v>
       </c>
       <c r="H25" t="n">
         <v>200</v>
       </c>
       <c r="I25" t="n">
-        <v>10.27</v>
+        <v>11.17</v>
       </c>
     </row>
     <row r="26">
@@ -1424,68 +1424,29 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BRAZIL 1</t>
+          <t>CHILE 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Botafogo FR</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Athletico-PR</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="G26" t="n">
-        <v>11.76</v>
+        <v>11.43</v>
       </c>
       <c r="H26" t="n">
         <v>200</v>
       </c>
       <c r="I26" t="n">
-        <v>11.17</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Lay 2x2</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>CHILE 2</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>San Luis</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Santiago Wanderers</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="G27" t="n">
-        <v>11.43</v>
-      </c>
-      <c r="H27" t="n">
-        <v>200</v>
-      </c>
-      <c r="I27" t="n">
         <v>10.86</v>
       </c>
     </row>
